--- a/gte/nodes/P/compressor_stage_parameters.xlsx
+++ b/gte/nodes/P/compressor_stage_parameters.xlsx
@@ -653,7 +653,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>48</v>
@@ -665,79 +665,79 @@
         <v>119.14879946912927</v>
       </c>
       <c r="F3">
-        <v>54.427938704640262</v>
+        <v>49.117895904187563</v>
       </c>
       <c r="G3">
         <v>46.370056793261561</v>
       </c>
       <c r="H3">
-        <v>3.953967464922127</v>
+        <v>4.65169367734614</v>
       </c>
       <c r="I3">
         <v>1.4238006004795234</v>
       </c>
       <c r="J3">
-        <v>0.16127003429954012</v>
+        <v>0.13430254624956445</v>
       </c>
       <c r="K3">
-        <v>0.28875426510224445</v>
+        <v>0.31001420709384764</v>
       </c>
       <c r="L3">
-        <v>89.026084493356848</v>
+        <v>68.691250624917174</v>
       </c>
       <c r="M3">
-        <v>31.256498622065426</v>
+        <v>29.316687066269935</v>
       </c>
       <c r="N3">
-        <v>8.9356792174603754</v>
+        <v>5.4544532290606416</v>
       </c>
       <c r="O3">
-        <v>5.63044489861471</v>
+        <v>5.6698356015131548</v>
       </c>
       <c r="P3">
-        <v>44.513042246678424</v>
+        <v>34.345625312458587</v>
       </c>
       <c r="Q3">
-        <v>15.628249311032713</v>
+        <v>14.658343533134968</v>
       </c>
       <c r="R3">
-        <v>88.7876198210119</v>
+        <v>108.95755479181983</v>
       </c>
       <c r="S3">
-        <v>50.625063036459792</v>
+        <v>41.0043885214544</v>
       </c>
       <c r="T3">
-        <v>100.21120349392908</v>
+        <v>124.52544951642048</v>
       </c>
       <c r="U3">
-        <v>221.14171734902556</v>
+        <v>235.42109888410062</v>
       </c>
       <c r="V3">
-        <v>1.5981102156268212</v>
+        <v>1.0819160669688077</v>
       </c>
       <c r="W3">
-        <v>0.60453839502688567</v>
+        <v>0.75148973218729265</v>
       </c>
       <c r="X3">
-        <v>0.031889226267887427</v>
+        <v>-0.2584155035965538</v>
       </c>
       <c r="Y3">
-        <v>0.74186482535520382</v>
+        <v>0.7113256815525415</v>
       </c>
       <c r="Z3">
-        <v>0.032927082146324504</v>
+        <v>0.012306645113335634</v>
       </c>
       <c r="AA3">
-        <v>0.26593848375158924</v>
+        <v>0.2738320255503397</v>
       </c>
       <c r="AB3">
-        <v>47.400132075319995</v>
+        <v>247.52635833268852</v>
       </c>
       <c r="AC3">
-        <v>3.0978921754060731</v>
+        <v>3.6075521613392958</v>
       </c>
       <c r="AD3">
-        <v>47.272423800487971</v>
+        <v>40.8755802334842</v>
       </c>
     </row>
   </sheetData>
@@ -1059,7 +1059,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>48</v>
@@ -1071,79 +1071,79 @@
         <v>133.29622272534618</v>
       </c>
       <c r="F3">
-        <v>99.887549538806027</v>
+        <v>90.142422754532276</v>
       </c>
       <c r="G3">
         <v>78.249992852185287</v>
       </c>
       <c r="H3">
-        <v>1.6430647975922725</v>
+        <v>2.0909636946292749</v>
       </c>
       <c r="I3">
         <v>-0.74133434819784683</v>
       </c>
       <c r="J3">
-        <v>0.29898615363926673</v>
+        <v>0.30469916001823494</v>
       </c>
       <c r="K3">
-        <v>0.31445717020075881</v>
+        <v>0.30716172854077189</v>
       </c>
       <c r="L3">
-        <v>39.182251425478661</v>
+        <v>25.792962631759607</v>
       </c>
       <c r="M3">
-        <v>27.955227964213815</v>
+        <v>35.627748927038</v>
       </c>
       <c r="N3">
-        <v>9.1001720802875212</v>
+        <v>5.7995001108643187</v>
       </c>
       <c r="O3">
-        <v>6.7353128300905585</v>
+        <v>8.3847229652335269</v>
       </c>
       <c r="P3">
-        <v>19.591125712739331</v>
+        <v>12.896481315879804</v>
       </c>
       <c r="Q3">
-        <v>13.977613982106908</v>
+        <v>17.813874463519</v>
       </c>
       <c r="R3">
-        <v>45.015969547914843</v>
+        <v>45.553438785867058</v>
       </c>
       <c r="S3">
-        <v>40.529113747604264</v>
+        <v>41.989984231328584</v>
       </c>
       <c r="T3">
-        <v>246.84378832451952</v>
+        <v>370.8410961013991</v>
       </c>
       <c r="U3">
-        <v>275.92674575564848</v>
+        <v>217.85707030343863</v>
       </c>
       <c r="V3">
-        <v>0.87861216520315477</v>
+        <v>0.791044776119403</v>
       </c>
       <c r="W3">
-        <v>0.79130949853947929</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>0.77276198457335643</v>
+        <v>0.6448191695715606</v>
       </c>
       <c r="Y3">
-        <v>0.67415452016117861</v>
+        <v>0.62859678932102026</v>
       </c>
       <c r="Z3">
-        <v>0.20017356005832457</v>
+        <v>0.15071399347315082</v>
       </c>
       <c r="AA3">
-        <v>0.16587029924904262</v>
+        <v>0.13442675974130539</v>
       </c>
       <c r="AB3">
-        <v>6.4383947263745913</v>
+        <v>6.252692639456586</v>
       </c>
       <c r="AC3">
-        <v>5.8921475935540339</v>
+        <v>9.8891450274401151</v>
       </c>
       <c r="AD3">
-        <v>72.1809463403849</v>
+        <v>76.902023595836226</v>
       </c>
     </row>
   </sheetData>
@@ -1465,7 +1465,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>48</v>
@@ -1477,79 +1477,79 @@
         <v>142.97855936295511</v>
       </c>
       <c r="F3">
-        <v>130.32675181840261</v>
+        <v>117.61194676294871</v>
       </c>
       <c r="G3">
         <v>100.46020452668535</v>
       </c>
       <c r="H3">
-        <v>1.0039543523158638</v>
+        <v>1.3827602282419034</v>
       </c>
       <c r="I3">
         <v>-1.441910504846335</v>
       </c>
       <c r="J3">
-        <v>0.36577048412294638</v>
+        <v>0.36697797289312445</v>
       </c>
       <c r="K3">
-        <v>0.35028120546100011</v>
+        <v>0.30426282938282367</v>
       </c>
       <c r="L3">
-        <v>3.7478967984058005</v>
+        <v>-1.3957137708292624</v>
       </c>
       <c r="M3">
-        <v>11.941033162174026</v>
+        <v>39.844323256313146</v>
       </c>
       <c r="N3">
-        <v>1.1579426896659415</v>
+        <v>-0.4109945651993242</v>
       </c>
       <c r="O3">
-        <v>3.5060678037794744</v>
+        <v>10.161946987298256</v>
       </c>
       <c r="P3">
-        <v>1.8739483992029002</v>
+        <v>-0.6978568854146312</v>
       </c>
       <c r="Q3">
-        <v>5.9705165810870131</v>
+        <v>19.922161628156573</v>
       </c>
       <c r="R3">
-        <v>21.398752228989867</v>
+        <v>21.797875873653091</v>
       </c>
       <c r="S3">
-        <v>27.394948492192427</v>
+        <v>43.108370667729865</v>
       </c>
       <c r="T3">
-        <v>2792.9582434973208</v>
+        <v>-7498.7523200345031</v>
       </c>
       <c r="U3">
-        <v>687.28665244288482</v>
+        <v>209.80396695626786</v>
       </c>
       <c r="V3">
-        <v>0.61775915779319435</v>
+        <v>0.66039956464088156</v>
       </c>
       <c r="W3">
-        <v>0.593986248320122</v>
+        <v>1.1640350576734373</v>
       </c>
       <c r="X3">
-        <v>0.64474395805171947</v>
+        <v>0.45727524053793089</v>
       </c>
       <c r="Y3">
-        <v>0.71885962652920754</v>
+        <v>0.5818769740960853</v>
       </c>
       <c r="Z3">
-        <v>0.24283589171355313</v>
+        <v>0.14159145584787153</v>
       </c>
       <c r="AA3">
-        <v>0.23920281884756672</v>
+        <v>0.093480738328228813</v>
       </c>
       <c r="AB3">
-        <v>0.39346867629614879</v>
+        <v>-1.5978510230721974</v>
       </c>
       <c r="AC3">
-        <v>1.3956190752037547</v>
+        <v>16.169202535128573</v>
       </c>
       <c r="AD3">
-        <v>3.8098751594709546</v>
+        <v>-236.76746654429118</v>
       </c>
     </row>
   </sheetData>
